--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-7.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94B2D01C-9131-4696-92F0-A275213B6B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93B11903-1232-44B5-A304-AF6E7DB29F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{F90A56F2-9180-4184-96A2-6EB5E7F5DA7F}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{D3C08E0C-D1D8-4F32-BB64-C77D0FBC01D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="191" r:id="rId3"/>
+    <pivotCache cacheId="223" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576919328705" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{17256117-C382-47E4-90CF-D95002CE1CC5}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579488888892" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{D8CF5C75-5450-4601-9E33-43F0C4218018}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BAD1D6DD-5794-43BF-8A02-D09CEB887415}" name="AllErrorPivot" cacheId="191" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C983760E-9B46-4590-A6AD-CB167A6B4489}" name="AllErrorPivot" cacheId="223" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -585,7 +585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C53F431-74C2-48C8-94A3-FB9F67EB60D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528C8CC4-706A-40EA-A09B-BC917D210557}">
   <dimension ref="A4:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -671,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58356AAC-5BA3-4397-AAC4-F6592CF2E4DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD46DDC3-66C2-430B-BF2A-58E79D8187B9}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
